--- a/samples/sample_2_dirty_errors.xlsx
+++ b/samples/sample_2_dirty_errors.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>774856838093</t>
+          <t>154021118406</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -523,27 +523,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>04.01.2004</t>
+          <t>03/05/2004</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+91 74637 71569</t>
+          <t>+91 89908 38246</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>08631063987</t>
+          <t>09252664624</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>634592634699</t>
+          <t>432066594059</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -610,22 +610,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11-01-2004</t>
+          <t>2004-05-18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+91 74713 17850</t>
+          <t>+91 81509 44328</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>07741725082</t>
+          <t>08257190928</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -660,12 +660,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>20-09-2026</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>427691334219</t>
+          <t>549646166855</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2006-05-02</t>
+          <t>2004-01-24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+91 99264 60220</t>
+          <t>+91 73251 33121</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>09399812805</t>
+          <t>08109707722</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>07.06.2026</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -769,17 +769,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2008-04-22</t>
+          <t>2007-05-14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+91 91292 95218</t>
+          <t>+91 95593 69607</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>08183630465</t>
+          <t>07464681992</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -824,24 +824,24 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>431668627350</t>
+          <t>409544558854</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -851,27 +851,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19.07.2004</t>
+          <t>04.05.2007</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+91 93511 61283</t>
+          <t>+91 83696 53927</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>08021590930</t>
+          <t>07180315863</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -911,12 +911,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>03/12/2005</t>
+          <t>22.12.2005</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+91 71454 17029</t>
+          <t>+91 97037 51982</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>08846666988</t>
+          <t>09486838368</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -993,19 +993,19 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>425437956182</t>
+          <t>439689002370</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>15.10.2008</t>
+          <t>10/07/2005</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+91 82652 23076</t>
+          <t>+91 78570 86470</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>08597068460</t>
+          <t>07584294556</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1093,12 +1093,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2004-02-23</t>
+          <t>2008-07-11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+91 76038 71851</t>
+          <t>+91 99221 65226</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>09117348339</t>
+          <t>09198733261</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1148,24 +1148,24 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>660348529498</t>
+          <t>711034197808</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1175,17 +1175,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>25/01/2007</t>
+          <t>04/01/2004</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+91 80199 99446</t>
+          <t>+91 86378 55221</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>07474038401</t>
+          <t>09441710817</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1230,24 +1230,24 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>573167559469</t>
+          <t>429871753442</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1267,17 +1267,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+91 84148 81191</t>
+          <t>+91 85011 44391</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>07099651897</t>
+          <t>07338549798</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1329,7 +1329,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>527322515085</t>
+          <t>240410767166</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1339,27 +1339,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2007-09-26</t>
+          <t>11-03-2008</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+91 74844 35323</t>
+          <t>+91 91655 31202</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>08108405473</t>
+          <t>07355996596</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1399,19 +1399,19 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>28-06-2026</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>212020554871</t>
+          <t>137470966471</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+91 85169 26461</t>
+          <t>+91 76095 92366</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>08200356137</t>
+          <t>07542275037</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>854461920326</t>
+          <t>471723325065</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1499,27 +1499,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2005-01-22</t>
+          <t>2005-06-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+91 74312 20961</t>
+          <t>+91 86127 53312</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>08551163422</t>
+          <t>09228722342</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1554,24 +1554,24 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>407707796082</t>
+          <t>752846868754</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1581,27 +1581,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2007-12-26</t>
+          <t>18-04-2007</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+91 86252 70166</t>
+          <t>+91 91093 77303</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>09053272997</t>
+          <t>09410467373</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>397786224228</t>
+          <t>525796123183</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1663,27 +1663,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2006-03-24</t>
+          <t>22-01-2005</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+91 73952 23837</t>
+          <t>+91 80573 10796</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>07731392256</t>
+          <t>09309615688</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1718,40 +1718,40 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>673013958365</t>
+          <t>598702514298</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2007-11-18</t>
+          <t>22.01.2008</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+91 71430 91176</t>
+          <t>+91 85866 94133</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>07839311271</t>
+          <t>08772095233</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1813,7 +1813,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>465935059010</t>
+          <t>548405009077</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1828,22 +1828,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2007-04-19</t>
+          <t>28/06/2005</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+91 98793 88844</t>
+          <t>+91 83126 95412</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>09660877375</t>
+          <t>08005011745</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>20-06-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>12.05.2008</t>
+          <t>05/03/2004</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+91 79586 52779</t>
+          <t>+91 72176 77267</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>07319994463</t>
+          <t>07751515787</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1956,24 +1956,24 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>13-09-2026</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>352763700014</t>
+          <t>344625460197</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1988,22 +1988,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2005-10-03</t>
+          <t>08-04-2008</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+91 96864 89447</t>
+          <t>+91 75564 59408</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>09214718570</t>
+          <t>07280347218</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>22.08.2026</t>
+          <t>20-09-2026</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2055,7 +2055,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>950453347060</t>
+          <t>340801129966</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2065,17 +2065,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>08/07/2008</t>
+          <t>2007-04-02</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+91 95679 87957</t>
+          <t>+91 94613 30972</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>09600982394</t>
+          <t>08618987629</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2137,7 +2137,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>224468875093</t>
+          <t>885499157188</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2147,27 +2147,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2004-04-27</t>
+          <t>2008-11-13</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+91 71236 81649</t>
+          <t>+91 97811 58597</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>09235128240</t>
+          <t>07691048617</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2207,19 +2207,19 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>224468875093</t>
+          <t>885499157188</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2229,27 +2229,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2004-04-27</t>
+          <t>2008-11-13</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+91 71236 81649</t>
+          <t>+91 97811 58597</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>09235128240</t>
+          <t>07691048617</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2289,19 +2289,19 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>184749587743</t>
+          <t>873565239134</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>24/09/2005</t>
+          <t>16.08.2008</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+91 78589 12146</t>
+          <t>+91 75792 84837</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>09152719041</t>
+          <t>08717117974</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2371,19 +2371,19 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>19-07-2026</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>721190470827</t>
+          <t>184775073747</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>02-12-2007</t>
+          <t>10.10.2005</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+91 82855 57779</t>
+          <t>+91 86712 59956</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>09903192898</t>
+          <t>07694330133</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2448,24 +2448,24 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>09-06-2026</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>939599460002</t>
+          <t>840302221338</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2475,17 +2475,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>18/05/2005</t>
+          <t>14/12/2008</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+91 78539 10706</t>
+          <t>+91 78476 49131</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>08478135735</t>
+          <t>09648271447</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2535,19 +2535,19 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>178198079602</t>
+          <t>353819606173</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>15.06.2007</t>
+          <t>2006-12-18</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+91 86604 42945</t>
+          <t>+91 95639 81572</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>08287762042</t>
+          <t>09510923225</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2612,24 +2612,24 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>187257469934</t>
+          <t>289246466072</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2644,22 +2644,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>09.09.2004</t>
+          <t>16/10/2005</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+91 96422 97164</t>
+          <t>+91 72200 42582</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>08926910794</t>
+          <t>09272234227</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>16-07-2026</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2711,7 +2711,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>487546569506</t>
+          <t>985968878127</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>28/03/2008</t>
+          <t>01-05-2005</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+91 86090 78769</t>
+          <t>+91 79175 82733</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>07911293436</t>
+          <t>09806255872</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>24.06.2026</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2793,7 +2793,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>470913443743</t>
+          <t>425170919969</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2004-12-06</t>
+          <t>10-09-2004</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+91 84201 39417</t>
+          <t>+91 93390 38037</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>09311321780</t>
+          <t>09452834226</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2875,7 +2875,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>830285341875</t>
+          <t>528156387479</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>10.08.2006</t>
+          <t>2008-10-21</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+91 70545 15588</t>
+          <t>+91 74139 57447</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>09103014364</t>
+          <t>08980412500</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -2975,7 +2975,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>152132669019</t>
+          <t>545003860477</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2985,27 +2985,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>14.06.2005</t>
+          <t>23-10-2007</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+91 90036 57958</t>
+          <t>+91 98288 63350</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>08894426413</t>
+          <t>07106545509</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3045,19 +3045,19 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>09-06-2026</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>684028523457</t>
+          <t>403600596366</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3072,22 +3072,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>03.12.2007</t>
+          <t>21/09/2007</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+91 93890 45445</t>
+          <t>+91 80056 87075</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>08937642453</t>
+          <t>07791632547</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3122,24 +3122,24 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>436242818443</t>
+          <t>370975227005</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3149,17 +3149,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2006-04-06</t>
+          <t>2007-07-05</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+91 95106 24487</t>
+          <t>+91 99054 87665</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>07373282639</t>
+          <t>09328324322</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3204,24 +3204,24 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>16-08-2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>311327910949</t>
+          <t>957329065257</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3231,27 +3231,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>07.10.2004</t>
+          <t>13-04-2008</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+91 85227 21312</t>
+          <t>+91 83610 59385</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>07902067573</t>
+          <t>08474283720</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3303,7 +3303,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>407086583983</t>
+          <t>285385839561</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10.10.2005</t>
+          <t>22/04/2004</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+91 72848 56284</t>
+          <t>+91 74155 41658</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>07360144046</t>
+          <t>09268029075</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>09.06.2026</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3385,7 +3385,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>920740112993</t>
+          <t>694260923137</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2007-12-02</t>
+          <t>22-09-2004</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+91 98076 50764</t>
+          <t>+91 72658 81328</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>07058937896</t>
+          <t>09384251781</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>30-07-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3467,7 +3467,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>237565537036</t>
+          <t>443357681475</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3477,27 +3477,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>25-12-2004</t>
+          <t>17/03/2007</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+91 79485 13761</t>
+          <t>+91 94070 41062</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>07953127562</t>
+          <t>09363951243</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3532,24 +3532,24 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>24.06.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>596930411623</t>
+          <t>537218272823</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3564,22 +3564,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>11.07.2004</t>
+          <t>03/08/2005</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+91 98836 35133</t>
+          <t>+91 98116 38080</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>07318702852</t>
+          <t>09659065706</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3614,24 +3614,24 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>22.08.2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>918742487108</t>
+          <t>975452993909</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3646,22 +3646,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2005-04-16</t>
+          <t>12-04-2008</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+91 90479 68350</t>
+          <t>+91 78247 89472</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>08298621663</t>
+          <t>08882901655</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3713,7 +3713,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>972073541356</t>
+          <t>333629863466</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,22 +3728,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>16-12-2004</t>
+          <t>2007-03-09</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+91 92514 22513</t>
+          <t>+91 88689 88459</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>09838390351</t>
+          <t>07731028688</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>19-06-2026</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -3795,7 +3795,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>499543112195</t>
+          <t>296452138712</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3810,22 +3810,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10-02-2008</t>
+          <t>15/12/2004</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+91 76997 60941</t>
+          <t>+91 81095 55178</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>07293965065</t>
+          <t>08827344323</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -3877,7 +3877,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>846427254240</t>
+          <t>567018524647</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3887,27 +3887,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>28/04/2005</t>
+          <t>07-06-2004</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+91 93471 85972</t>
+          <t>+91 82420 10195</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>09928264073</t>
+          <t>07301676797</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3942,24 +3942,24 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>898209459461</t>
+          <t>926774261900</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3969,17 +3969,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2008-06-27</t>
+          <t>2005-11-03</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+91 70573 69972</t>
+          <t>+91 70786 10102</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>09917838350</t>
+          <t>08990104365</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4029,19 +4029,19 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>28-06-2026</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>983878091884</t>
+          <t>664881047425</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>27.04.2004</t>
+          <t>2004-03-18</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+91 76552 20652</t>
+          <t>+91 88413 51101</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>08702169766</t>
+          <t>08075830842</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>13-06-2026</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4123,7 +4123,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>894368115297</t>
+          <t>733301061749</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4133,12 +4133,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2005-03-22</t>
+          <t>03.06.2004</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+91 98728 83119</t>
+          <t>+91 72625 22515</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>07518065894</t>
+          <t>09967006878</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4193,19 +4193,19 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>08-08-2026</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>366775139652</t>
+          <t>811966050128</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4215,27 +4215,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>14/02/2008</t>
+          <t>23-06-2006</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+91 85686 22446</t>
+          <t>+91 79218 73820</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>07039213420</t>
+          <t>08032250768</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4270,17 +4270,17 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>

--- a/samples/sample_2_dirty_errors.xlsx
+++ b/samples/sample_2_dirty_errors.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>154021118406</t>
+          <t>407707796082</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -528,22 +528,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>03/05/2004</t>
+          <t>2007-12-26</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+91 89908 38246</t>
+          <t>+91 86252 70166</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>09252664624</t>
+          <t>09053272997</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>432066594059</t>
+          <t>397786224228</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2004-05-18</t>
+          <t>2006-03-24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -620,12 +620,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+91 81509 44328</t>
+          <t>+91 73952 23837</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>08257190928</t>
+          <t>07731392256</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -660,12 +660,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>20-09-2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>549646166855</t>
+          <t>673013958365</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2004-01-24</t>
+          <t>2007-11-18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+91 73251 33121</t>
+          <t>+91 71430 91176</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>08109707722</t>
+          <t>07839311271</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
@@ -769,27 +769,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2007-05-14</t>
+          <t>2007-04-19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+91 95593 69607</t>
+          <t>+91 98793 88844</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>07464681992</t>
+          <t>09660877375</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -824,24 +824,24 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>20-06-2026</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>409544558854</t>
+          <t>811297619405</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -851,27 +851,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>04.05.2007</t>
+          <t>12.05.2008</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+91 83696 53927</t>
+          <t>+91 79586 52779</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>07180315863</t>
+          <t>07319994463</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -933,12 +933,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>22.12.2005</t>
+          <t>2005-10-03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+91 97037 51982</t>
+          <t>+91 96864 89447</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>09486838368</t>
+          <t>09214718570</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>22.08.2026</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1005,7 +1005,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>439689002370</t>
+          <t>950453347060</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10/07/2005</t>
+          <t>08/07/2008</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+91 78570 86470</t>
+          <t>+91 95679 87957</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>07584294556</t>
+          <t>09600982394</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
@@ -1093,17 +1093,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2008-07-11</t>
+          <t>2004-04-27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+91 99221 65226</t>
+          <t>+91 71236 81649</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>09198733261</t>
+          <t>09235128240</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1153,19 +1153,19 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>711034197808</t>
+          <t>184749587743</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>04/01/2004</t>
+          <t>24/09/2005</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+91 86378 55221</t>
+          <t>+91 78589 12146</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>09441710817</t>
+          <t>09152719041</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1235,19 +1235,19 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>19-07-2026</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>429871753442</t>
+          <t>721190470827</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+91 85011 44391</t>
+          <t>+91 82855 57779</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>07338549798</t>
+          <t>09903192898</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1329,7 +1329,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>240410767166</t>
+          <t>939599460002</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1339,27 +1339,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11-03-2008</t>
+          <t>18/05/2005</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+91 91655 31202</t>
+          <t>+91 78539 10706</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>07355996596</t>
+          <t>08478135735</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1399,19 +1399,19 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>28-06-2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>137470966471</t>
+          <t>178198079602</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1421,13 +1421,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+91 76095 92366</t>
+          <t>+91 86604 42945</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>07542275037</t>
+          <t>08287762042</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>28-09-2026</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>471723325065</t>
+          <t>187257469934</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1499,27 +1499,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2005-06-12</t>
+          <t>09.09.2004</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+91 86127 53312</t>
+          <t>+91 96422 97164</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>09228722342</t>
+          <t>08926910794</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>16-07-2026</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1571,7 +1571,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>752846868754</t>
+          <t>487546569506</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1581,27 +1581,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>18-04-2007</t>
+          <t>28/03/2008</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+91 91093 77303</t>
+          <t>+91 86090 78769</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>09410467373</t>
+          <t>07911293436</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>525796123183</t>
+          <t>470913443743</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1668,22 +1668,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>22-01-2005</t>
+          <t>2004-12-06</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+91 80573 10796</t>
+          <t>+91 84201 39417</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>09309615688</t>
+          <t>09311321780</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1723,19 +1723,19 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>598702514298</t>
+          <t>830285341875</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>22.01.2008</t>
+          <t>10.08.2006</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+91 85866 94133</t>
+          <t>+91 70545 15588</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>08772095233</t>
+          <t>09103014364</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1796,24 +1796,24 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>548405009077</t>
+          <t>152132669019</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1823,27 +1823,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>28/06/2005</t>
+          <t>14.06.2005</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+91 83126 95412</t>
+          <t>+91 90036 57958</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>08005011745</t>
+          <t>08894426413</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>05/03/2004</t>
+          <t>03.12.2007</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+91 72176 77267</t>
+          <t>+91 93890 45445</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>07751515787</t>
+          <t>08937642453</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>13-09-2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1973,7 +1973,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>344625460197</t>
+          <t>436242818443</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1983,27 +1983,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>08-04-2008</t>
+          <t>2006-04-06</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+91 75564 59408</t>
+          <t>+91 95106 24487</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>07280347218</t>
+          <t>07373282639</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2038,12 +2038,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>20-09-2026</t>
+          <t>16-08-2026</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2055,7 +2055,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>340801129966</t>
+          <t>311327910949</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2065,27 +2065,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2007-04-02</t>
+          <t>07.10.2004</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+91 94613 30972</t>
+          <t>+91 85227 21312</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>08618987629</t>
+          <t>07902067573</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2120,24 +2120,24 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>885499157188</t>
+          <t>407086583983</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2147,27 +2147,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2008-11-13</t>
+          <t>10.10.2005</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+91 97811 58597</t>
+          <t>+91 72848 56284</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>07691048617</t>
+          <t>07360144046</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2202,24 +2202,24 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>885499157188</t>
+          <t>407086583983</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2229,27 +2229,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2008-11-13</t>
+          <t>10.10.2005</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+91 97811 58597</t>
+          <t>+91 72848 56284</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>07691048617</t>
+          <t>07360144046</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2284,24 +2284,24 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>873565239134</t>
+          <t>920740112993</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2311,17 +2311,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>16.08.2008</t>
+          <t>2007-12-02</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+91 75792 84837</t>
+          <t>+91 98076 50764</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>08717117974</t>
+          <t>07058937896</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2366,24 +2366,24 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>30-07-2026</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>184775073747</t>
+          <t>237565537036</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2393,27 +2393,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10.10.2005</t>
+          <t>25-12-2004</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+91 86712 59956</t>
+          <t>+91 79485 13761</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>07694330133</t>
+          <t>07953127562</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2448,24 +2448,24 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>09-06-2026</t>
+          <t>24.06.2026</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>840302221338</t>
+          <t>596930411623</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>14/12/2008</t>
+          <t>11.07.2004</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+91 78476 49131</t>
+          <t>+91 98836 35133</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>09648271447</t>
+          <t>07318702852</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2535,19 +2535,19 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>22.08.2026</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>353819606173</t>
+          <t>918742487108</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2562,22 +2562,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2006-12-18</t>
+          <t>2005-04-16</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+91 95639 81572</t>
+          <t>+91 90479 68350</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>09510923225</t>
+          <t>08298621663</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2617,19 +2617,19 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>289246466072</t>
+          <t>972073541356</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>16/10/2005</t>
+          <t>16-12-2004</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2654,12 +2654,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+91 72200 42582</t>
+          <t>+91 92514 22513</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>09272234227</t>
+          <t>09838390351</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2694,24 +2694,24 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>985968878127</t>
+          <t>499543112195</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2721,27 +2721,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>01-05-2005</t>
+          <t>10-02-2008</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+91 79175 82733</t>
+          <t>+91 76997 60941</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>09806255872</t>
+          <t>07293965065</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2776,12 +2776,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2793,7 +2793,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>425170919969</t>
+          <t>846427254240</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2808,22 +2808,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10-09-2004</t>
+          <t>28/04/2005</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+91 93390 38037</t>
+          <t>+91 93471 85972</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>09452834226</t>
+          <t>09928264073</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2863,19 +2863,19 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>528156387479</t>
+          <t>898209459461</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2890,22 +2890,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2008-10-21</t>
+          <t>2008-06-27</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+91 74139 57447</t>
+          <t>+91 70573 69972</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>08980412500</t>
+          <t>09917838350</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>28-06-2026</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -2975,7 +2975,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>545003860477</t>
+          <t>983878091884</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2985,27 +2985,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>23-10-2007</t>
+          <t>27.04.2004</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+91 98288 63350</t>
+          <t>+91 76552 20652</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>07106545509</t>
+          <t>08702169766</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3040,24 +3040,24 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>09-06-2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>403600596366</t>
+          <t>894368115297</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3072,22 +3072,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>21/09/2007</t>
+          <t>2005-03-22</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+91 80056 87075</t>
+          <t>+91 98728 83119</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>07791632547</t>
+          <t>07518065894</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3122,24 +3122,24 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>370975227005</t>
+          <t>366775139652</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3154,22 +3154,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2007-07-05</t>
+          <t>14/02/2008</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+91 99054 87665</t>
+          <t>+91 85686 22446</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>09328324322</t>
+          <t>07039213420</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3221,7 +3221,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>957329065257</t>
+          <t>559802307048</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3231,17 +3231,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>13-04-2008</t>
+          <t>10.07.2007</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+91 83610 59385</t>
+          <t>+91 91081 43066</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>08474283720</t>
+          <t>07842306981</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>26.06.2026</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3303,7 +3303,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>285385839561</t>
+          <t>174993076187</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3313,27 +3313,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>22/04/2004</t>
+          <t>11.04.2006</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+91 74155 41658</t>
+          <t>+91 71228 96146</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>09268029075</t>
+          <t>09771745179</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3373,19 +3373,19 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>09.06.2026</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>694260923137</t>
+          <t>958622714206</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3395,27 +3395,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>22-09-2004</t>
+          <t>08/07/2004</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+91 72658 81328</t>
+          <t>+91 70891 71914</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>09384251781</t>
+          <t>08889973873</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3450,24 +3450,24 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>443357681475</t>
+          <t>297320279630</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3477,27 +3477,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>17/03/2007</t>
+          <t>16/07/2004</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+91 94070 41062</t>
+          <t>+91 75427 63430</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>09363951243</t>
+          <t>09387890161</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3532,24 +3532,24 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>537218272823</t>
+          <t>841570170004</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3559,17 +3559,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>03/08/2005</t>
+          <t>04/09/2004</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+91 98116 38080</t>
+          <t>+91 76768 62248</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>09659065706</t>
+          <t>08169062330</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3631,7 +3631,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>975452993909</t>
+          <t>483743439232</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,27 +3641,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>12-04-2008</t>
+          <t>28.02.2006</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+91 78247 89472</t>
+          <t>+91 88356 62369</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>08882901655</t>
+          <t>09808194359</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>20-07-2026</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3713,7 +3713,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>333629863466</t>
+          <t>222171363401</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3723,17 +3723,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2007-03-09</t>
+          <t>2006-12-09</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+91 88689 88459</t>
+          <t>+91 83395 75390</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>07731028688</t>
+          <t>07340723305</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3778,24 +3778,24 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>19-06-2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>296452138712</t>
+          <t>755880323867</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3805,17 +3805,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>15/12/2004</t>
+          <t>2008-03-04</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+91 81095 55178</t>
+          <t>+91 92209 30392</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>08827344323</t>
+          <t>07859284446</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3865,19 +3865,19 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>567018524647</t>
+          <t>989776854627</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3887,27 +3887,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>07-06-2004</t>
+          <t>2007-11-24</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+91 82420 10195</t>
+          <t>+91 98322 19694</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>07301676797</t>
+          <t>08992480741</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3942,24 +3942,24 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>926774261900</t>
+          <t>866175130152</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3969,17 +3969,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2005-11-03</t>
+          <t>2008-11-23</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+91 70786 10102</t>
+          <t>+91 85682 13548</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>08990104365</t>
+          <t>08717584946</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4041,7 +4041,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>664881047425</t>
+          <t>267157263062</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4051,27 +4051,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2004-03-18</t>
+          <t>09.07.2007</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+91 88413 51101</t>
+          <t>+91 94644 65462</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>08075830842</t>
+          <t>07694700384</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4106,24 +4106,24 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>13-06-2026</t>
+          <t>19.07.2026</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>733301061749</t>
+          <t>552079585617</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4133,17 +4133,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>03.06.2004</t>
+          <t>24.03.2004</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+91 72625 22515</t>
+          <t>+91 73601 42702</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>09967006878</t>
+          <t>09685777135</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4188,24 +4188,24 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>08-08-2026</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>811966050128</t>
+          <t>397185108519</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>23-06-2006</t>
+          <t>23.12.2006</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4230,12 +4230,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+91 79218 73820</t>
+          <t>+91 81143 95417</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>08032250768</t>
+          <t>09660587587</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4270,17 +4270,17 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>26.07.2026</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>

--- a/samples/sample_2_dirty_errors.xlsx
+++ b/samples/sample_2_dirty_errors.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>407707796082</t>
+          <t>786373350822</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -523,27 +523,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2007-12-26</t>
+          <t>12/04/2006</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+91 86252 70166</t>
+          <t>+91 97776 67338</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>09053272997</t>
+          <t>09467324934</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>397786224228</t>
+          <t>711020403133</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -605,17 +605,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2006-03-24</t>
+          <t>2008-01-14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+91 73952 23837</t>
+          <t>+91 92562 74557</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>07731392256</t>
+          <t>07340563178</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -665,19 +665,19 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>673013958365</t>
+          <t>462371002625</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2007-11-18</t>
+          <t>24-01-2004</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+91 71430 91176</t>
+          <t>+91 95921 89379</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>07839311271</t>
+          <t>08435644196</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -742,12 +742,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>26-09-2026</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -769,27 +769,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2007-04-19</t>
+          <t>01.10.2005</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+91 98793 88844</t>
+          <t>+91 74661 72396</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>09660877375</t>
+          <t>07311240558</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>20-06-2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>811297619405</t>
+          <t>595544477878</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -851,17 +851,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12.05.2008</t>
+          <t>04.03.2005</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+91 79586 52779</t>
+          <t>+91 79648 54116</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>07319994463</t>
+          <t>08873086258</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -933,17 +933,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2005-10-03</t>
+          <t>15-05-2004</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+91 96864 89447</t>
+          <t>+91 76976 92903</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>09214718570</t>
+          <t>08345324306</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>22.08.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1005,7 +1005,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>950453347060</t>
+          <t>410570826663</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1015,17 +1015,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>08/07/2008</t>
+          <t>16-07-2008</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+91 95679 87957</t>
+          <t>+91 79314 44584</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>09600982394</t>
+          <t>07809642225</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
@@ -1093,17 +1093,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2004-04-27</t>
+          <t>2004-04-11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+91 71236 81649</t>
+          <t>+91 97506 18045</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>09235128240</t>
+          <t>09311242529</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1148,24 +1148,24 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>184749587743</t>
+          <t>489574942730</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1175,17 +1175,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>24/09/2005</t>
+          <t>10.07.2008</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+91 78589 12146</t>
+          <t>+91 93345 47802</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>09152719041</t>
+          <t>09250449560</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>19-07-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>721190470827</t>
+          <t>259665633768</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+91 82855 57779</t>
+          <t>+91 96828 22515</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>09903192898</t>
+          <t>09226794717</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1329,7 +1329,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>939599460002</t>
+          <t>466017347670</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>18/05/2005</t>
+          <t>23/09/2005</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+91 78539 10706</t>
+          <t>+91 80183 21473</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>08478135735</t>
+          <t>08924270785</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>178198079602</t>
+          <t>223018514600</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+91 86604 42945</t>
+          <t>+91 84017 25403</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>08287762042</t>
+          <t>08528173370</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1472,24 +1472,24 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>187257469934</t>
+          <t>774856838093</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1499,27 +1499,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>09.09.2004</t>
+          <t>04.01.2004</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+91 96422 97164</t>
+          <t>+91 74637 71569</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>08926910794</t>
+          <t>08631063987</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1554,24 +1554,24 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>16-07-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>487546569506</t>
+          <t>634592634699</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1581,27 +1581,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>28/03/2008</t>
+          <t>11-01-2004</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+91 86090 78769</t>
+          <t>+91 74713 17850</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>07911293436</t>
+          <t>07741725082</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>470913443743</t>
+          <t>427691334219</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1663,17 +1663,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2004-12-06</t>
+          <t>2006-05-02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+91 84201 39417</t>
+          <t>+91 99264 60220</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>09311321780</t>
+          <t>09399812805</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>07.06.2026</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1735,23 +1735,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>830285341875</t>
+          <t>957792614967</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10.08.2006</t>
+          <t>2008-04-22</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+91 70545 15588</t>
+          <t>+91 91292 95218</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>09103014364</t>
+          <t>08183630465</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1801,19 +1801,19 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>152132669019</t>
+          <t>431668627350</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1828,22 +1828,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>14.06.2005</t>
+          <t>19.07.2004</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+91 90036 57958</t>
+          <t>+91 93511 61283</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>08894426413</t>
+          <t>08021590930</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>03.12.2007</t>
+          <t>03/12/2005</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+91 93890 45445</t>
+          <t>+91 71454 17029</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>08937642453</t>
+          <t>08846666988</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1956,24 +1956,24 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>436242818443</t>
+          <t>425437956182</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1983,27 +1983,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2006-04-06</t>
+          <t>15.10.2008</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+91 95106 24487</t>
+          <t>+91 82652 23076</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>07373282639</t>
+          <t>08597068460</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>16-08-2026</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2055,7 +2055,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>311327910949</t>
+          <t>445965346770</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>07.10.2004</t>
+          <t>2004-02-23</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+91 85227 21312</t>
+          <t>+91 76038 71851</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>07902067573</t>
+          <t>09117348339</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2120,24 +2120,24 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>407086583983</t>
+          <t>660348529498</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10.10.2005</t>
+          <t>25/01/2007</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+91 72848 56284</t>
+          <t>+91 80199 99446</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>07360144046</t>
+          <t>07474038401</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2219,7 +2219,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>407086583983</t>
+          <t>660348529498</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10.10.2005</t>
+          <t>25/01/2007</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+91 72848 56284</t>
+          <t>+91 80199 99446</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>07360144046</t>
+          <t>07474038401</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2301,7 +2301,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>920740112993</t>
+          <t>573167559469</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2311,17 +2311,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2007-12-02</t>
+          <t>2005-09-07</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+91 98076 50764</t>
+          <t>+91 84148 81191</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>07058937896</t>
+          <t>07099651897</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>30-07-2026</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>237565537036</t>
+          <t>527322515085</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>25-12-2004</t>
+          <t>2007-09-26</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+91 79485 13761</t>
+          <t>+91 74844 35323</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>07953127562</t>
+          <t>08108405473</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2448,24 +2448,24 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>24.06.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>596930411623</t>
+          <t>212020554871</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2480,22 +2480,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>11.07.2004</t>
+          <t>2004-07-06</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+91 98836 35133</t>
+          <t>+91 85169 26461</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>07318702852</t>
+          <t>08200356137</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2530,24 +2530,24 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>22.08.2026</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>918742487108</t>
+          <t>854461920326</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2562,22 +2562,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2005-04-16</t>
+          <t>2005-01-22</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+91 90479 68350</t>
+          <t>+91 74312 20961</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>08298621663</t>
+          <t>08551163422</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2612,24 +2612,24 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>972073541356</t>
+          <t>407707796082</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>16-12-2004</t>
+          <t>2007-12-26</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+91 92514 22513</t>
+          <t>+91 86252 70166</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>09838390351</t>
+          <t>09053272997</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2711,7 +2711,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>499543112195</t>
+          <t>397786224228</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2721,27 +2721,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10-02-2008</t>
+          <t>2006-03-24</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+91 76997 60941</t>
+          <t>+91 73952 23837</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>07293965065</t>
+          <t>07731392256</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2793,7 +2793,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>846427254240</t>
+          <t>673013958365</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2803,27 +2803,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>28/04/2005</t>
+          <t>2007-11-18</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+91 93471 85972</t>
+          <t>+91 71430 91176</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>09928264073</t>
+          <t>07839311271</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2875,7 +2875,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>898209459461</t>
+          <t>465935059010</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2008-06-27</t>
+          <t>2007-04-19</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+91 70573 69972</t>
+          <t>+91 98793 88844</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>09917838350</t>
+          <t>09660877375</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>28-06-2026</t>
+          <t>20-06-2026</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>983878091884</t>
+          <t>811297619405</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2985,17 +2985,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>27.04.2004</t>
+          <t>12.05.2008</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+91 76552 20652</t>
+          <t>+91 79586 52779</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>08702169766</t>
+          <t>07319994463</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3040,24 +3040,24 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>894368115297</t>
+          <t>352763700014</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3067,17 +3067,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2005-03-22</t>
+          <t>2005-10-03</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+91 98728 83119</t>
+          <t>+91 96864 89447</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>07518065894</t>
+          <t>09214718570</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>22.08.2026</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3139,7 +3139,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>366775139652</t>
+          <t>950453347060</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>14/02/2008</t>
+          <t>08/07/2008</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+91 85686 22446</t>
+          <t>+91 95679 87957</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>07039213420</t>
+          <t>09600982394</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3221,7 +3221,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>559802307048</t>
+          <t>224468875093</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3236,22 +3236,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>10.07.2007</t>
+          <t>2004-04-27</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+91 91081 43066</t>
+          <t>+91 71236 81649</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>07842306981</t>
+          <t>09235128240</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3291,19 +3291,19 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>26.06.2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>174993076187</t>
+          <t>184749587743</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3313,27 +3313,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>11.04.2006</t>
+          <t>24/09/2005</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+91 71228 96146</t>
+          <t>+91 78589 12146</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>09771745179</t>
+          <t>09152719041</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3368,24 +3368,24 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>19-07-2026</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>958622714206</t>
+          <t>721190470827</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>08/07/2004</t>
+          <t>02-12-2007</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+91 70891 71914</t>
+          <t>+91 82855 57779</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>08889973873</t>
+          <t>09903192898</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3450,24 +3450,24 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>297320279630</t>
+          <t>939599460002</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3477,27 +3477,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>16/07/2004</t>
+          <t>18/05/2005</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+91 75427 63430</t>
+          <t>+91 78539 10706</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>09387890161</t>
+          <t>08478135735</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3532,24 +3532,24 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>841570170004</t>
+          <t>178198079602</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3559,27 +3559,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>04/09/2004</t>
+          <t>15.06.2007</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+91 76768 62248</t>
+          <t>+91 86604 42945</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>08169062330</t>
+          <t>08287762042</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>28-09-2026</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3631,7 +3631,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>483743439232</t>
+          <t>187257469934</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3646,22 +3646,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>28.02.2006</t>
+          <t>09.09.2004</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+91 88356 62369</t>
+          <t>+91 96422 97164</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>09808194359</t>
+          <t>08926910794</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>20-07-2026</t>
+          <t>16-07-2026</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3713,7 +3713,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>222171363401</t>
+          <t>487546569506</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3723,27 +3723,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2006-12-09</t>
+          <t>28/03/2008</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+91 83395 75390</t>
+          <t>+91 86090 78769</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>07340723305</t>
+          <t>07911293436</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3783,19 +3783,19 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>24.06.2026</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>755880323867</t>
+          <t>470913443743</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3805,27 +3805,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2008-03-04</t>
+          <t>2004-12-06</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+91 92209 30392</t>
+          <t>+91 84201 39417</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>07859284446</t>
+          <t>09311321780</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3865,19 +3865,19 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>989776854627</t>
+          <t>830285341875</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2007-11-24</t>
+          <t>10.08.2006</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3902,12 +3902,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+91 98322 19694</t>
+          <t>+91 70545 15588</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>08992480741</t>
+          <t>09103014364</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3947,19 +3947,19 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>866175130152</t>
+          <t>152132669019</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3969,12 +3969,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2008-11-23</t>
+          <t>14.06.2005</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+91 85682 13548</t>
+          <t>+91 90036 57958</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>08717584946</t>
+          <t>08894426413</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4029,19 +4029,19 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>267157263062</t>
+          <t>684028523457</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>09.07.2007</t>
+          <t>03.12.2007</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+91 94644 65462</t>
+          <t>+91 93890 45445</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>07694700384</t>
+          <t>08937642453</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4111,19 +4111,19 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>19.07.2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>552079585617</t>
+          <t>436242818443</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4133,12 +4133,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>24.03.2004</t>
+          <t>2006-04-06</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4148,12 +4148,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+91 73601 42702</t>
+          <t>+91 95106 24487</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>09685777135</t>
+          <t>07373282639</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>16-08-2026</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4205,7 +4205,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>397185108519</t>
+          <t>311327910949</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4215,17 +4215,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>23.12.2006</t>
+          <t>07.10.2004</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+91 81143 95417</t>
+          <t>+91 85227 21312</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>09660587587</t>
+          <t>07902067573</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4270,17 +4270,17 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>

--- a/samples/sample_2_dirty_errors.xlsx
+++ b/samples/sample_2_dirty_errors.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>786373350822</t>
+          <t>407707796082</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -523,27 +523,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12/04/2006</t>
+          <t>2007-12-26</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+91 97776 67338</t>
+          <t>+91 86252 70166</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>09467324934</t>
+          <t>09053272997</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>711020403133</t>
+          <t>397786224228</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -605,17 +605,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2008-01-14</t>
+          <t>2006-03-24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+91 92562 74557</t>
+          <t>+91 73952 23837</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>07340563178</t>
+          <t>07731392256</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -665,19 +665,19 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>462371002625</t>
+          <t>673013958365</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>24-01-2004</t>
+          <t>2007-11-18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+91 95921 89379</t>
+          <t>+91 71430 91176</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>08435644196</t>
+          <t>07839311271</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -742,12 +742,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>26-09-2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -769,27 +769,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>01.10.2005</t>
+          <t>2007-04-19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+91 74661 72396</t>
+          <t>+91 98793 88844</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>07311240558</t>
+          <t>09660877375</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>20-06-2026</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>595544477878</t>
+          <t>811297619405</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -851,17 +851,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>04.03.2005</t>
+          <t>12.05.2008</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+91 79648 54116</t>
+          <t>+91 79586 52779</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>08873086258</t>
+          <t>07319994463</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -933,17 +933,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15-05-2004</t>
+          <t>2005-10-03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+91 76976 92903</t>
+          <t>+91 96864 89447</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>08345324306</t>
+          <t>09214718570</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>22.08.2026</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1005,7 +1005,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>410570826663</t>
+          <t>950453347060</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1015,17 +1015,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16-07-2008</t>
+          <t>08/07/2008</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+91 79314 44584</t>
+          <t>+91 95679 87957</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>07809642225</t>
+          <t>09600982394</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
@@ -1093,17 +1093,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2004-04-11</t>
+          <t>2004-04-27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+91 97506 18045</t>
+          <t>+91 71236 81649</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>09311242529</t>
+          <t>09235128240</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1148,24 +1148,24 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>489574942730</t>
+          <t>184749587743</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1175,17 +1175,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10.07.2008</t>
+          <t>24/09/2005</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+91 93345 47802</t>
+          <t>+91 78589 12146</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>09250449560</t>
+          <t>09152719041</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>19-07-2026</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>259665633768</t>
+          <t>721190470827</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+91 96828 22515</t>
+          <t>+91 82855 57779</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>09226794717</t>
+          <t>09903192898</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1329,7 +1329,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>466017347670</t>
+          <t>939599460002</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>23/09/2005</t>
+          <t>18/05/2005</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+91 80183 21473</t>
+          <t>+91 78539 10706</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>08924270785</t>
+          <t>08478135735</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>223018514600</t>
+          <t>178198079602</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+91 84017 25403</t>
+          <t>+91 86604 42945</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>08528173370</t>
+          <t>08287762042</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1472,24 +1472,24 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>28-09-2026</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>774856838093</t>
+          <t>187257469934</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1499,27 +1499,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>04.01.2004</t>
+          <t>09.09.2004</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+91 74637 71569</t>
+          <t>+91 96422 97164</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>08631063987</t>
+          <t>08926910794</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1554,24 +1554,24 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>16-07-2026</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>634592634699</t>
+          <t>487546569506</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1581,27 +1581,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>11-01-2004</t>
+          <t>28/03/2008</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+91 74713 17850</t>
+          <t>+91 86090 78769</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>07741725082</t>
+          <t>07911293436</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>427691334219</t>
+          <t>470913443743</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1663,17 +1663,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2006-05-02</t>
+          <t>2004-12-06</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+91 99264 60220</t>
+          <t>+91 84201 39417</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>09399812805</t>
+          <t>09311321780</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>07.06.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1735,23 +1735,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>957792614967</t>
+          <t>830285341875</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2008-04-22</t>
+          <t>10.08.2006</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+91 91292 95218</t>
+          <t>+91 70545 15588</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>08183630465</t>
+          <t>09103014364</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1801,19 +1801,19 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>431668627350</t>
+          <t>152132669019</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1828,22 +1828,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>19.07.2004</t>
+          <t>14.06.2005</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+91 93511 61283</t>
+          <t>+91 90036 57958</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>08021590930</t>
+          <t>08894426413</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>03/12/2005</t>
+          <t>03.12.2007</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+91 71454 17029</t>
+          <t>+91 93890 45445</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>08846666988</t>
+          <t>08937642453</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1956,24 +1956,24 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>425437956182</t>
+          <t>436242818443</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1983,27 +1983,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>15.10.2008</t>
+          <t>2006-04-06</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+91 82652 23076</t>
+          <t>+91 95106 24487</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>08597068460</t>
+          <t>07373282639</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>16-08-2026</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2055,7 +2055,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>445965346770</t>
+          <t>311327910949</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2004-02-23</t>
+          <t>07.10.2004</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+91 76038 71851</t>
+          <t>+91 85227 21312</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>09117348339</t>
+          <t>07902067573</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2120,24 +2120,24 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>660348529498</t>
+          <t>407086583983</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>25/01/2007</t>
+          <t>10.10.2005</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+91 80199 99446</t>
+          <t>+91 72848 56284</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>07474038401</t>
+          <t>07360144046</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2219,7 +2219,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>660348529498</t>
+          <t>407086583983</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>25/01/2007</t>
+          <t>10.10.2005</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+91 80199 99446</t>
+          <t>+91 72848 56284</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>07474038401</t>
+          <t>07360144046</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2301,7 +2301,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>573167559469</t>
+          <t>920740112993</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2311,17 +2311,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2005-09-07</t>
+          <t>2007-12-02</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+91 84148 81191</t>
+          <t>+91 98076 50764</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>07099651897</t>
+          <t>07058937896</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>30-07-2026</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>527322515085</t>
+          <t>237565537036</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2007-09-26</t>
+          <t>25-12-2004</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+91 74844 35323</t>
+          <t>+91 79485 13761</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>08108405473</t>
+          <t>07953127562</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2448,24 +2448,24 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>24.06.2026</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>212020554871</t>
+          <t>596930411623</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2480,22 +2480,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2004-07-06</t>
+          <t>11.07.2004</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+91 85169 26461</t>
+          <t>+91 98836 35133</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>08200356137</t>
+          <t>07318702852</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2530,24 +2530,24 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>22.08.2026</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>854461920326</t>
+          <t>918742487108</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2562,22 +2562,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2005-01-22</t>
+          <t>2005-04-16</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+91 74312 20961</t>
+          <t>+91 90479 68350</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>08551163422</t>
+          <t>08298621663</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2612,24 +2612,24 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>407707796082</t>
+          <t>972073541356</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2007-12-26</t>
+          <t>16-12-2004</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+91 86252 70166</t>
+          <t>+91 92514 22513</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>09053272997</t>
+          <t>09838390351</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2711,7 +2711,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>397786224228</t>
+          <t>499543112195</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2721,27 +2721,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2006-03-24</t>
+          <t>10-02-2008</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+91 73952 23837</t>
+          <t>+91 76997 60941</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>07731392256</t>
+          <t>07293965065</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2793,7 +2793,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>673013958365</t>
+          <t>846427254240</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2803,27 +2803,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2007-11-18</t>
+          <t>28/04/2005</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+91 71430 91176</t>
+          <t>+91 93471 85972</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>07839311271</t>
+          <t>09928264073</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2875,7 +2875,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>465935059010</t>
+          <t>898209459461</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2007-04-19</t>
+          <t>2008-06-27</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+91 98793 88844</t>
+          <t>+91 70573 69972</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>09660877375</t>
+          <t>09917838350</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>20-06-2026</t>
+          <t>28-06-2026</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>811297619405</t>
+          <t>983878091884</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2985,17 +2985,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>12.05.2008</t>
+          <t>27.04.2004</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+91 79586 52779</t>
+          <t>+91 76552 20652</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>07319994463</t>
+          <t>08702169766</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3040,24 +3040,24 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>352763700014</t>
+          <t>894368115297</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3067,17 +3067,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2005-10-03</t>
+          <t>2005-03-22</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+91 96864 89447</t>
+          <t>+91 98728 83119</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>09214718570</t>
+          <t>07518065894</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>22.08.2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3139,7 +3139,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>950453347060</t>
+          <t>366775139652</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>08/07/2008</t>
+          <t>14/02/2008</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+91 95679 87957</t>
+          <t>+91 85686 22446</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>09600982394</t>
+          <t>07039213420</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3221,7 +3221,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>224468875093</t>
+          <t>559802307048</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3236,22 +3236,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2004-04-27</t>
+          <t>10.07.2007</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+91 71236 81649</t>
+          <t>+91 91081 43066</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>09235128240</t>
+          <t>07842306981</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3291,19 +3291,19 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>26.06.2026</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>184749587743</t>
+          <t>174993076187</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3313,27 +3313,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>24/09/2005</t>
+          <t>11.04.2006</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+91 78589 12146</t>
+          <t>+91 71228 96146</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>09152719041</t>
+          <t>09771745179</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3368,24 +3368,24 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>19-07-2026</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>721190470827</t>
+          <t>958622714206</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>02-12-2007</t>
+          <t>08/07/2004</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+91 82855 57779</t>
+          <t>+91 70891 71914</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>09903192898</t>
+          <t>08889973873</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3450,24 +3450,24 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>939599460002</t>
+          <t>297320279630</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3477,27 +3477,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>18/05/2005</t>
+          <t>16/07/2004</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+91 78539 10706</t>
+          <t>+91 75427 63430</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>08478135735</t>
+          <t>09387890161</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3532,24 +3532,24 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>178198079602</t>
+          <t>841570170004</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3559,27 +3559,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>15.06.2007</t>
+          <t>04/09/2004</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+91 86604 42945</t>
+          <t>+91 76768 62248</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>08287762042</t>
+          <t>08169062330</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3631,7 +3631,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>187257469934</t>
+          <t>483743439232</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3646,22 +3646,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>09.09.2004</t>
+          <t>28.02.2006</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+91 96422 97164</t>
+          <t>+91 88356 62369</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>08926910794</t>
+          <t>09808194359</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>16-07-2026</t>
+          <t>20-07-2026</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3713,7 +3713,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>487546569506</t>
+          <t>222171363401</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3723,27 +3723,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>28/03/2008</t>
+          <t>2006-12-09</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+91 86090 78769</t>
+          <t>+91 83395 75390</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>07911293436</t>
+          <t>07340723305</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3783,19 +3783,19 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>24.06.2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>470913443743</t>
+          <t>755880323867</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3805,27 +3805,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2004-12-06</t>
+          <t>2008-03-04</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+91 84201 39417</t>
+          <t>+91 92209 30392</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>09311321780</t>
+          <t>07859284446</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3865,19 +3865,19 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>830285341875</t>
+          <t>989776854627</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>10.08.2006</t>
+          <t>2007-11-24</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3902,12 +3902,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+91 70545 15588</t>
+          <t>+91 98322 19694</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>09103014364</t>
+          <t>08992480741</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3947,19 +3947,19 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>152132669019</t>
+          <t>866175130152</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3969,12 +3969,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>14.06.2005</t>
+          <t>2008-11-23</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+91 90036 57958</t>
+          <t>+91 85682 13548</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>08894426413</t>
+          <t>08717584946</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4029,19 +4029,19 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>684028523457</t>
+          <t>267157263062</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>03.12.2007</t>
+          <t>09.07.2007</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+91 93890 45445</t>
+          <t>+91 94644 65462</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>08937642453</t>
+          <t>07694700384</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4111,19 +4111,19 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>19.07.2026</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>436242818443</t>
+          <t>552079585617</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4133,12 +4133,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2006-04-06</t>
+          <t>24.03.2004</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4148,12 +4148,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+91 95106 24487</t>
+          <t>+91 73601 42702</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>07373282639</t>
+          <t>09685777135</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>16-08-2026</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4205,7 +4205,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>311327910949</t>
+          <t>397185108519</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4215,17 +4215,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>07.10.2004</t>
+          <t>23.12.2006</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+91 85227 21312</t>
+          <t>+91 81143 95417</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>07902067573</t>
+          <t>09660587587</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4270,17 +4270,17 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>26.07.2026</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>

--- a/samples/sample_2_dirty_errors.xlsx
+++ b/samples/sample_2_dirty_errors.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>407707796082</t>
+          <t>372693176556</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -528,12 +528,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2007-12-26</t>
+          <t>15-05-2004</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+91 86252 70166</t>
+          <t>+91 76976 92903</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>09053272997</t>
+          <t>08345324306</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>397786224228</t>
+          <t>410570826663</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -605,27 +605,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2006-03-24</t>
+          <t>16-07-2008</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+91 73952 23837</t>
+          <t>+91 79314 44584</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>07731392256</t>
+          <t>07809642225</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>673013958365</t>
+          <t>688907959686</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -692,22 +692,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2007-11-18</t>
+          <t>2004-04-11</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+91 71430 91176</t>
+          <t>+91 97506 18045</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>07839311271</t>
+          <t>09311242529</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -742,17 +742,17 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2007-04-19</t>
+          <t>10.07.2008</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+91 98793 88844</t>
+          <t>+91 93345 47802</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>09660877375</t>
+          <t>09250449560</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>20-06-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>811297619405</t>
+          <t>259665633768</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -851,27 +851,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12.05.2008</t>
+          <t>22-04-2008</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+91 79586 52779</t>
+          <t>+91 96828 22515</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>07319994463</t>
+          <t>09226794717</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2005-10-03</t>
+          <t>23/09/2005</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+91 96864 89447</t>
+          <t>+91 80183 21473</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>09214718570</t>
+          <t>08924270785</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>22.08.2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1005,7 +1005,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>950453347060</t>
+          <t>223018514600</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>08/07/2008</t>
+          <t>22.04.2004</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+91 95679 87957</t>
+          <t>+91 84017 25403</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>09600982394</t>
+          <t>08528173370</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2004-04-27</t>
+          <t>04.01.2004</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+91 71236 81649</t>
+          <t>+91 74637 71569</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>09235128240</t>
+          <t>08631063987</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1148,24 +1148,24 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>184749587743</t>
+          <t>634592634699</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1175,17 +1175,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>24/09/2005</t>
+          <t>11-01-2004</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+91 78589 12146</t>
+          <t>+91 74713 17850</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>09152719041</t>
+          <t>07741725082</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1230,24 +1230,24 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>19-07-2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>721190470827</t>
+          <t>427691334219</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1267,17 +1267,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+91 82855 57779</t>
+          <t>+91 99264 60220</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>09903192898</t>
+          <t>09399812805</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1312,24 +1312,24 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>07.06.2026</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>939599460002</t>
+          <t>957792614967</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>18/05/2005</t>
+          <t>2008-04-22</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+91 78539 10706</t>
+          <t>+91 91292 95218</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>08478135735</t>
+          <t>08183630465</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1394,24 +1394,24 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>178198079602</t>
+          <t>431668627350</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1421,13 +1421,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+91 86604 42945</t>
+          <t>+91 93511 61283</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>08287762042</t>
+          <t>08021590930</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1472,24 +1472,24 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>187257469934</t>
+          <t>816562753200</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1499,27 +1499,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>09.09.2004</t>
+          <t>03/12/2005</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+91 96422 97164</t>
+          <t>+91 71454 17029</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>08926910794</t>
+          <t>08846666988</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>16-07-2026</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1571,7 +1571,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>487546569506</t>
+          <t>425437956182</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1586,22 +1586,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>28/03/2008</t>
+          <t>15.10.2008</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+91 86090 78769</t>
+          <t>+91 82652 23076</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>07911293436</t>
+          <t>08597068460</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>470913443743</t>
+          <t>445965346770</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1663,27 +1663,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2004-12-06</t>
+          <t>2004-02-23</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+91 84201 39417</t>
+          <t>+91 76038 71851</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>09311321780</t>
+          <t>09117348339</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1718,35 +1718,35 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>830285341875</t>
+          <t>660348529498</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10.08.2006</t>
+          <t>25/01/2007</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+91 70545 15588</t>
+          <t>+91 80199 99446</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>09103014364</t>
+          <t>07474038401</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1801,19 +1801,19 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>152132669019</t>
+          <t>573167559469</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1823,17 +1823,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>14.06.2005</t>
+          <t>2005-09-07</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+91 90036 57958</t>
+          <t>+91 84148 81191</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>08894426413</t>
+          <t>07099651897</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1878,17 +1878,17 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>03.12.2007</t>
+          <t>2007-09-26</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+91 93890 45445</t>
+          <t>+91 74844 35323</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>08937642453</t>
+          <t>08108405473</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1973,7 +1973,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>436242818443</t>
+          <t>212020554871</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1988,22 +1988,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2006-04-06</t>
+          <t>2004-07-06</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+91 95106 24487</t>
+          <t>+91 85169 26461</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>07373282639</t>
+          <t>08200356137</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2038,24 +2038,24 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>16-08-2026</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>311327910949</t>
+          <t>854461920326</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2065,27 +2065,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>07.10.2004</t>
+          <t>2005-01-22</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+91 85227 21312</t>
+          <t>+91 74312 20961</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>07902067573</t>
+          <t>08551163422</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2137,7 +2137,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>407086583983</t>
+          <t>407707796082</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2147,27 +2147,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10.10.2005</t>
+          <t>2007-12-26</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+91 72848 56284</t>
+          <t>+91 86252 70166</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>07360144046</t>
+          <t>09053272997</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2202,24 +2202,24 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>407086583983</t>
+          <t>407707796082</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2229,27 +2229,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10.10.2005</t>
+          <t>2007-12-26</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+91 72848 56284</t>
+          <t>+91 86252 70166</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>07360144046</t>
+          <t>09053272997</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2284,24 +2284,24 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>920740112993</t>
+          <t>397786224228</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2007-12-02</t>
+          <t>2006-03-24</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+91 98076 50764</t>
+          <t>+91 73952 23837</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>07058937896</t>
+          <t>07731392256</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2371,19 +2371,19 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>30-07-2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>237565537036</t>
+          <t>673013958365</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2393,27 +2393,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>25-12-2004</t>
+          <t>2007-11-18</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+91 79485 13761</t>
+          <t>+91 71430 91176</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>07953127562</t>
+          <t>07839311271</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>24.06.2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2465,7 +2465,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>596930411623</t>
+          <t>465935059010</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>11.07.2004</t>
+          <t>2007-04-19</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+91 98836 35133</t>
+          <t>+91 98793 88844</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>07318702852</t>
+          <t>09660877375</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2535,19 +2535,19 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>22.08.2026</t>
+          <t>20-06-2026</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>918742487108</t>
+          <t>811297619405</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2005-04-16</t>
+          <t>12.05.2008</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+91 90479 68350</t>
+          <t>+91 79586 52779</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>08298621663</t>
+          <t>07319994463</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2629,7 +2629,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>972073541356</t>
+          <t>352763700014</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2639,17 +2639,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>16-12-2004</t>
+          <t>2005-10-03</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+91 92514 22513</t>
+          <t>+91 96864 89447</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>09838390351</t>
+          <t>09214718570</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>22.08.2026</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2711,7 +2711,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>499543112195</t>
+          <t>950453347060</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10-02-2008</t>
+          <t>08/07/2008</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+91 76997 60941</t>
+          <t>+91 95679 87957</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>07293965065</t>
+          <t>09600982394</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2781,19 +2781,19 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>846427254240</t>
+          <t>224468875093</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>28/04/2005</t>
+          <t>2004-04-27</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+91 93471 85972</t>
+          <t>+91 71236 81649</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>09928264073</t>
+          <t>09235128240</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2875,7 +2875,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>898209459461</t>
+          <t>184749587743</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2885,17 +2885,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2008-06-27</t>
+          <t>24/09/2005</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+91 70573 69972</t>
+          <t>+91 78589 12146</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>09917838350</t>
+          <t>09152719041</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2940,17 +2940,17 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>28-06-2026</t>
+          <t>19-07-2026</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>983878091884</t>
+          <t>721190470827</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2985,27 +2985,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>27.04.2004</t>
+          <t>02-12-2007</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+91 76552 20652</t>
+          <t>+91 82855 57779</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>08702169766</t>
+          <t>09903192898</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3045,19 +3045,19 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>894368115297</t>
+          <t>939599460002</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3067,27 +3067,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2005-03-22</t>
+          <t>18/05/2005</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+91 98728 83119</t>
+          <t>+91 78539 10706</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>07518065894</t>
+          <t>08478135735</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3139,7 +3139,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>366775139652</t>
+          <t>178198079602</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3149,27 +3149,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>14/02/2008</t>
+          <t>15.06.2007</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+91 85686 22446</t>
+          <t>+91 86604 42945</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>07039213420</t>
+          <t>08287762042</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3221,7 +3221,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>559802307048</t>
+          <t>187257469934</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>10.07.2007</t>
+          <t>09.09.2004</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+91 91081 43066</t>
+          <t>+91 96422 97164</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>07842306981</t>
+          <t>08926910794</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3291,19 +3291,19 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>26.06.2026</t>
+          <t>16-07-2026</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>174993076187</t>
+          <t>487546569506</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3313,27 +3313,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>11.04.2006</t>
+          <t>28/03/2008</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+91 71228 96146</t>
+          <t>+91 86090 78769</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>09771745179</t>
+          <t>07911293436</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>24.06.2026</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3385,7 +3385,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>958622714206</t>
+          <t>470913443743</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3395,27 +3395,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>08/07/2004</t>
+          <t>2004-12-06</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+91 70891 71914</t>
+          <t>+91 84201 39417</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>08889973873</t>
+          <t>09311321780</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3467,7 +3467,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>297320279630</t>
+          <t>830285341875</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3482,22 +3482,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>16/07/2004</t>
+          <t>10.08.2006</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+91 75427 63430</t>
+          <t>+91 70545 15588</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>09387890161</t>
+          <t>09103014364</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3532,24 +3532,24 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>841570170004</t>
+          <t>152132669019</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3564,22 +3564,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>04/09/2004</t>
+          <t>14.06.2005</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+91 76768 62248</t>
+          <t>+91 90036 57958</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>08169062330</t>
+          <t>08894426413</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3614,24 +3614,24 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>483743439232</t>
+          <t>684028523457</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>28.02.2006</t>
+          <t>03.12.2007</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+91 88356 62369</t>
+          <t>+91 93890 45445</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>09808194359</t>
+          <t>08937642453</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3696,24 +3696,24 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>20-07-2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>222171363401</t>
+          <t>436242818443</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3723,17 +3723,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2006-12-09</t>
+          <t>2006-04-06</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+91 83395 75390</t>
+          <t>+91 95106 24487</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>07340723305</t>
+          <t>07373282639</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3778,24 +3778,24 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>16-08-2026</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>755880323867</t>
+          <t>311327910949</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3805,12 +3805,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2008-03-04</t>
+          <t>07.10.2004</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+91 92209 30392</t>
+          <t>+91 85227 21312</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>07859284446</t>
+          <t>07902067573</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3860,24 +3860,24 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>989776854627</t>
+          <t>407086583983</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3887,27 +3887,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2007-11-24</t>
+          <t>10.10.2005</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+91 98322 19694</t>
+          <t>+91 72848 56284</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>08992480741</t>
+          <t>07360144046</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -3959,7 +3959,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>866175130152</t>
+          <t>920740112993</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2008-11-23</t>
+          <t>2007-12-02</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+91 85682 13548</t>
+          <t>+91 98076 50764</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>08717584946</t>
+          <t>07058937896</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>30-07-2026</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4041,7 +4041,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>267157263062</t>
+          <t>237565537036</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4051,27 +4051,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>09.07.2007</t>
+          <t>25-12-2004</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+91 94644 65462</t>
+          <t>+91 79485 13761</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>07694700384</t>
+          <t>07953127562</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>19.07.2026</t>
+          <t>24.06.2026</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4123,7 +4123,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>552079585617</t>
+          <t>596930411623</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4133,27 +4133,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>24.03.2004</t>
+          <t>11.07.2004</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+91 73601 42702</t>
+          <t>+91 98836 35133</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>09685777135</t>
+          <t>07318702852</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>22.08.2026</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4205,7 +4205,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>397185108519</t>
+          <t>918742487108</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4215,27 +4215,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>23.12.2006</t>
+          <t>2005-04-16</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+91 81143 95417</t>
+          <t>+91 90479 68350</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>09660587587</t>
+          <t>08298621663</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
